--- a/UMBRAMED_GrantApplicationsTracker.xlsx
+++ b/UMBRAMED_GrantApplicationsTracker.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>DRAFT IN PROGRESS</t>
+          <t>BLOCKED - PARTNER NEEDED</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Missing third-country partner</t>
+          <t>No third-country partner, budget incomplete, ethics incomplete</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Find third partner, finish Part B, complete budget and ethics sections</t>
+          <t>Do not submit until third eligible partner is added</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>READY TO SUBMIT</t>
+          <t>READY - LOGIN REQUIRED</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Appendices package still needed</t>
+          <t>Portal authentication required</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>Finalize PDFs and complete portal submission</t>
+          <t>Log into IFS, upload appendices, review finances, submit</t>
         </is>
       </c>
       <c r="N4" s="4" t="inlineStr">

--- a/UMBRAMED_GrantApplicationsTracker.xlsx
+++ b/UMBRAMED_GrantApplicationsTracker.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -876,6 +876,162 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Eurostars Call 10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Eurostars-3 Call 10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>International SME R&amp;D project</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CONDITIONAL - LEGAL CHECKS NEEDED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Agents AI Ltd</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Eurostars portal / national bodies</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Call 10</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-03-19 14:00 Brussels</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>National funding by country</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Sami + Valerio</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Need immediate SME eligibility/account filings confirmation for Spain and UK</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Only submit if both entities are eligible SMEs and dossier can be assembled immediately</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>GRANT_APPLICATIONS_STATUS.md</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Potentially real, but only with same-week legal/financial confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EIT Health Innovation Validation Call 2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EIT Health Innovation Validation Call 2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Consortium validation grant</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OPEN - NOT READY</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Agents AI Ltd</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EIT Health application portal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Up to EUR 850,000, max 50% co-funding</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Sami + Valerio</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Missing research/education partner and IML6 evidence pack</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Treat as next-wave target after partner and maturity evidence are assembled</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>GRANT_APPLICATIONS_STATUS.md</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Open call with real fit, but not immediate from current repo assets</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
